--- a/artfynd/A 21810-2026 artfynd.xlsx
+++ b/artfynd/A 21810-2026 artfynd.xlsx
@@ -2279,7 +2279,7 @@
         <v>134457400</v>
       </c>
       <c r="B15" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
